--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -5,21 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stud\Documents\sarmat\HEI_info_system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\HEI_info_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A07BE914-7712-4435-B66F-12C1DA81E72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C82B96-FABA-4F7C-92CB-77351E5A95DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{DCD8AE47-C61E-4767-B3AD-DAF7BAA64D5F}"/>
+    <workbookView xWindow="6540" yWindow="2295" windowWidth="18120" windowHeight="13305" xr2:uid="{DCD8AE47-C61E-4767-B3AD-DAF7BAA64D5F}"/>
   </bookViews>
   <sheets>
     <sheet name="students" sheetId="1" r:id="rId1"/>
-    <sheet name="groups" sheetId="2" r:id="rId2"/>
-    <sheet name="teachers" sheetId="3" r:id="rId3"/>
-    <sheet name="schedules" sheetId="4" r:id="rId4"/>
-    <sheet name="science_works" sheetId="5" r:id="rId5"/>
-    <sheet name="auth" sheetId="6" r:id="rId6"/>
-    <sheet name="sessions" sheetId="7" r:id="rId7"/>
+    <sheet name="disciplines" sheetId="8" r:id="rId2"/>
+    <sheet name="groups" sheetId="2" r:id="rId3"/>
+    <sheet name="teachers" sheetId="3" r:id="rId4"/>
+    <sheet name="schedules" sheetId="4" r:id="rId5"/>
+    <sheet name="science_works" sheetId="5" r:id="rId6"/>
+    <sheet name="auth" sheetId="6" r:id="rId7"/>
+    <sheet name="sessions" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>surname</t>
   </si>
@@ -118,6 +119,12 @@
   </si>
   <si>
     <t>last_auth</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>code</t>
   </si>
 </sst>
 </file>
@@ -470,8 +477,126 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC12EA5-B280-42D6-A9A9-C440A3DA6959}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3355C60-A4DC-4EB0-8CB4-B970A68304E8}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02E049-4A43-4922-AC5F-DED9F56E59FA}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2423D60-6650-4EC6-BE8E-39C7C092B509}">
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -487,19 +612,19 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -507,75 +632,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02E049-4A43-4922-AC5F-DED9F56E59FA}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2423D60-6650-4EC6-BE8E-39C7C092B509}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9891187C-5BC9-4216-BD9D-B9108381423F}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -594,10 +658,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{035D892E-4928-491A-8C9A-7D4CF506A2CA}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -618,10 +687,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA278FF-83F4-4656-8EE9-AC172AAB7F4C}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -642,10 +717,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C62953B-0C7A-46E2-9FE0-EF1B373AC45F}">
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
